--- a/data/satisfaction_detail/2026/1-8月/参展商.xlsx
+++ b/data/satisfaction_detail/2026/1-8月/参展商.xlsx
@@ -472,10 +472,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>9.640000000000001</v>
+        <v>9.61761101384689</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>9.91</v>
+        <v>9.918111305639556</v>
       </c>
     </row>
     <row r="3">
@@ -485,10 +485,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>9.91</v>
+        <v>9.922304101013317</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>9.98</v>
+        <v>9.974503156666136</v>
       </c>
     </row>
     <row r="4">
@@ -498,10 +498,10 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>9.99</v>
+        <v>9.991596371160274</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>9.99</v>
+        <v>9.985118573929652</v>
       </c>
     </row>
     <row r="5">
@@ -511,10 +511,10 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>10</v>
+        <v>9.998511857392964</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>10</v>
+        <v>9.995535572178895</v>
       </c>
     </row>
     <row r="6">
@@ -537,10 +537,10 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>9.640000000000001</v>
+        <v>9.692752931189984</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>9.9</v>
+        <v>9.910442994323306</v>
       </c>
     </row>
     <row r="8">
@@ -561,10 +561,10 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>9.24</v>
+        <v>9.219364422515785</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.802117884237891</v>
       </c>
     </row>
     <row r="10">
@@ -574,10 +574,10 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>8.539999999999999</v>
+        <v>8.443087166427928</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>9.66</v>
+        <v>9.622309406334553</v>
       </c>
     </row>
     <row r="11">
@@ -587,10 +587,10 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>9.470000000000001</v>
+        <v>9.474854368932039</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>9.84</v>
+        <v>9.847094806090508</v>
       </c>
     </row>
     <row r="12">
@@ -600,10 +600,10 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>9.130000000000001</v>
+        <v>9.086029497586079</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>9.73</v>
+        <v>9.743771022335403</v>
       </c>
     </row>
     <row r="13">
@@ -613,10 +613,10 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>9.27</v>
+        <v>9.28215767414717</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>9.82</v>
+        <v>9.841358162236725</v>
       </c>
     </row>
     <row r="14">
@@ -626,10 +626,10 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>9.15</v>
+        <v>9.151580985728685</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>9.76</v>
+        <v>9.775115390736909</v>
       </c>
     </row>
     <row r="15">
@@ -639,10 +639,10 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>9.869999999999999</v>
+        <v>9.878392487665128</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>9.98</v>
+        <v>9.978763329619609</v>
       </c>
     </row>
     <row r="16">
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>9.76</v>
+        <v>9.712325852830388</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>9.949999999999999</v>
+        <v>9.974999204201815</v>
       </c>
     </row>
     <row r="17">
@@ -665,10 +665,10 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>9.210000000000001</v>
+        <v>9.143896227916601</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.899996816807258</v>
       </c>
     </row>
     <row r="18">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>9.83</v>
+        <v>9.736842105263159</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>10</v>
